--- a/course-design-2/outputs/tables/ch8/33_F_group_ablation.xlsx
+++ b/course-design-2/outputs/tables/ch8/33_F_group_ablation.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_消融结果" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_增量与bootstrap" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_与Stage15复现对照" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_方法与口径" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_方法与统计范围" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_F特征清单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_未来泄漏审计" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_特征维度对照" sheetId="7" state="visible" r:id="rId7"/>
